--- a/Check.xlsx
+++ b/Check.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diman\Desktop\Диплом\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{157EFD5A-A91A-42BC-A200-A64D5825A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC95157F-C90E-4349-99E7-73C37E572338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="66">
   <si>
     <t>Группа проверок/модуль</t>
   </si>
@@ -215,13 +215,16 @@
   </si>
   <si>
     <t>Открытие Правил использования</t>
+  </si>
+  <si>
+    <t>Авторизация в приложении с невалидными логином и паролем (ввод символов)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -254,6 +257,11 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -388,8 +396,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -403,19 +412,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{ED3B7320-4245-4C46-BD87-F8248A03B14D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -639,7 +649,7 @@
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,8 +660,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -662,7 +672,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="10"/>
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -671,7 +681,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -680,16 +690,16 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="4" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -699,8 +709,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+    <row r="7" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
       <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
@@ -708,8 +718,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
+    <row r="8" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
@@ -717,8 +727,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
+    <row r="9" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
       <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
@@ -726,8 +736,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+    <row r="10" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
       <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
@@ -735,8 +745,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+    <row r="11" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
@@ -745,7 +755,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -756,7 +766,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
@@ -765,7 +775,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
@@ -774,7 +784,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
@@ -783,7 +793,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="4" t="s">
         <v>22</v>
       </c>
@@ -791,8 +801,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
+    <row r="17" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
       <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
@@ -801,7 +811,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
+      <c r="A18" s="10"/>
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
@@ -810,7 +820,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="4" t="s">
         <v>25</v>
       </c>
@@ -819,7 +829,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="4" t="s">
         <v>26</v>
       </c>
@@ -828,7 +838,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
@@ -837,7 +847,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
+      <c r="A22" s="10"/>
       <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
@@ -845,8 +855,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
+    <row r="23" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
       <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
@@ -854,8 +864,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
+    <row r="24" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
       <c r="B24" s="6" t="s">
         <v>29</v>
       </c>
@@ -863,8 +873,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
+    <row r="25" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
       <c r="B25" s="6" t="s">
         <v>30</v>
       </c>
@@ -872,8 +882,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
+    <row r="26" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
       <c r="B26" s="6" t="s">
         <v>31</v>
       </c>
@@ -882,7 +892,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
+      <c r="A27" s="10"/>
       <c r="B27" s="6" t="s">
         <v>32</v>
       </c>
@@ -890,8 +900,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
+    <row r="28" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
       <c r="B28" s="6" t="s">
         <v>33</v>
       </c>
@@ -899,8 +909,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
+    <row r="29" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
       <c r="B29" s="6" t="s">
         <v>34</v>
       </c>
@@ -908,8 +918,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+    <row r="30" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -919,8 +929,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
+    <row r="31" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
       <c r="B31" s="6" t="s">
         <v>37</v>
       </c>
@@ -928,8 +938,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
+    <row r="32" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
       <c r="B32" s="6" t="s">
         <v>38</v>
       </c>
@@ -937,8 +947,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
+    <row r="33" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
       <c r="B33" s="6" t="s">
         <v>39</v>
       </c>
@@ -947,7 +957,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
+      <c r="A34" s="12"/>
       <c r="B34" s="6" t="s">
         <v>40</v>
       </c>
@@ -956,7 +966,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
+      <c r="A35" s="12"/>
       <c r="B35" s="6" t="s">
         <v>41</v>
       </c>
@@ -964,8 +974,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
+    <row r="36" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
       <c r="B36" s="6" t="s">
         <v>42</v>
       </c>
@@ -973,8 +983,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
+    <row r="37" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A37" s="8"/>
       <c r="B37" s="6" t="s">
         <v>43</v>
       </c>
@@ -982,8 +992,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+    <row r="38" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -993,8 +1003,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="11"/>
+    <row r="39" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
       <c r="B39" s="6" t="s">
         <v>46</v>
       </c>
@@ -1002,8 +1012,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
+    <row r="40" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
       <c r="B40" s="6" t="s">
         <v>47</v>
       </c>
@@ -1011,8 +1021,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="11"/>
+    <row r="41" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
       <c r="B41" s="6" t="s">
         <v>48</v>
       </c>
@@ -1020,8 +1030,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="11"/>
+    <row r="42" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A42" s="12"/>
       <c r="B42" s="6" t="s">
         <v>49</v>
       </c>
@@ -1029,8 +1039,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="11"/>
+    <row r="43" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
       <c r="B43" s="6" t="s">
         <v>50</v>
       </c>
@@ -1038,8 +1048,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="11"/>
+    <row r="44" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A44" s="12"/>
       <c r="B44" s="6" t="s">
         <v>51</v>
       </c>
@@ -1047,8 +1057,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="11"/>
+    <row r="45" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
       <c r="B45" s="6" t="s">
         <v>52</v>
       </c>
@@ -1057,7 +1067,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11"/>
+      <c r="A46" s="12"/>
       <c r="B46" s="6" t="s">
         <v>53</v>
       </c>
@@ -1066,7 +1076,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11"/>
+      <c r="A47" s="12"/>
       <c r="B47" s="6" t="s">
         <v>54</v>
       </c>
@@ -1075,7 +1085,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11"/>
+      <c r="A48" s="12"/>
       <c r="B48" s="6" t="s">
         <v>55</v>
       </c>
@@ -1084,7 +1094,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11"/>
+      <c r="A49" s="12"/>
       <c r="B49" s="6" t="s">
         <v>56</v>
       </c>
@@ -1093,7 +1103,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11"/>
+      <c r="A50" s="12"/>
       <c r="B50" s="6" t="s">
         <v>57</v>
       </c>
@@ -1102,7 +1112,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11"/>
+      <c r="A51" s="12"/>
       <c r="B51" s="6" t="s">
         <v>58</v>
       </c>
@@ -1111,7 +1121,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="11"/>
+      <c r="A52" s="12"/>
       <c r="B52" s="6" t="s">
         <v>59</v>
       </c>
@@ -1120,7 +1130,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
+      <c r="A53" s="12"/>
       <c r="B53" s="4" t="s">
         <v>26</v>
       </c>
@@ -1129,7 +1139,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="11"/>
+      <c r="A54" s="12"/>
       <c r="B54" s="4" t="s">
         <v>60</v>
       </c>
@@ -1138,7 +1148,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="8"/>
       <c r="B55" s="4" t="s">
         <v>61</v>
       </c>
@@ -1146,8 +1156,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+    <row r="56" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
         <v>62</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -1157,8 +1167,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+    <row r="57" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A57" s="8"/>
       <c r="B57" s="6" t="s">
         <v>64</v>
       </c>

--- a/Check.xlsx
+++ b/Check.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diman\Desktop\Диплом\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC95157F-C90E-4349-99E7-73C37E572338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7C26A9-5700-46D0-AA75-D7701DB9A6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="68">
   <si>
     <t>Группа проверок/модуль</t>
   </si>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t>Авторизация в приложении с невалидными логином и паролем (ввод символов)</t>
+  </si>
+  <si>
+    <t>Цитаты</t>
+  </si>
+  <si>
+    <t>Разворачивание/сворачивание цитат</t>
   </si>
 </sst>
 </file>
@@ -291,7 +297,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -395,12 +401,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -422,6 +443,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -641,7 +676,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -1168,16 +1203,35 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A57" s="8"/>
-      <c r="B57" s="6" t="s">
+      <c r="A57" s="12"/>
+      <c r="B57" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="C57" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="18"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A11"/>
@@ -1186,7 +1240,7 @@
     <mergeCell ref="A38:A55"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C57" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C58" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
